--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_encounters_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_bootstrap_summary_encounters_SOURCE.xlsx
@@ -506,13 +506,13 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>6.376</v>
+        <v>6.378</v>
       </c>
       <c r="D4">
         <v>0.003</v>
       </c>
       <c r="E4">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="F4">
         <v>0.002</v>
@@ -521,19 +521,19 @@
         <v>6.276</v>
       </c>
       <c r="H4">
-        <v>6.484</v>
+        <v>6.48</v>
       </c>
       <c r="I4">
-        <v>6.275</v>
+        <v>6.277</v>
       </c>
       <c r="J4">
-        <v>6.48</v>
+        <v>6.482</v>
       </c>
       <c r="K4">
-        <v>6.276</v>
+        <v>6.273</v>
       </c>
       <c r="L4">
-        <v>6.481</v>
+        <v>6.478</v>
       </c>
     </row>
     <row r="5">
@@ -546,7 +546,7 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>1.735</v>
+        <v>1.737</v>
       </c>
       <c r="D5">
         <v>0.001</v>
@@ -558,22 +558,22 @@
         <v>0.001</v>
       </c>
       <c r="G5">
+        <v>1.678</v>
+      </c>
+      <c r="H5">
+        <v>1.796</v>
+      </c>
+      <c r="I5">
+        <v>1.677</v>
+      </c>
+      <c r="J5">
+        <v>1.794</v>
+      </c>
+      <c r="K5">
         <v>1.68</v>
       </c>
-      <c r="H5">
-        <v>1.798</v>
-      </c>
-      <c r="I5">
-        <v>1.68</v>
-      </c>
-      <c r="J5">
-        <v>1.796</v>
-      </c>
-      <c r="K5">
-        <v>1.678</v>
-      </c>
       <c r="L5">
-        <v>1.794</v>
+        <v>1.797</v>
       </c>
     </row>
   </sheetData>
